--- a/options.xlsx
+++ b/options.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\Tipificador Mejor\Primigenio - soporte Hogar\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\Hogar-main(2)\Hogar-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD470007-4104-4057-B918-3AF69C3B3565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{233C41B5-88DF-4608-9A36-CE594345DD24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="118">
   <si>
     <t>option_key</t>
   </si>
@@ -340,6 +340,57 @@
   </si>
   <si>
     <t>Luces Verdes (sin intermitencia); Luz Roja (LOS); Luz (Power  encendida) Sola; Luz Pon (Intermitente); Sin Luces encendidas en la (ONT)</t>
+  </si>
+  <si>
+    <t>Sondeo</t>
+  </si>
+  <si>
+    <t>son</t>
+  </si>
+  <si>
+    <t>inconvenientes</t>
+  </si>
+  <si>
+    <t>Inconvenientes</t>
+  </si>
+  <si>
+    <t>reason</t>
+  </si>
+  <si>
+    <t>Razón</t>
+  </si>
+  <si>
+    <t>¿Algún inconveniente?</t>
+  </si>
+  <si>
+    <t>¿Razón de comunicación?</t>
+  </si>
+  <si>
+    <t>Por servicio de internet; Por servicio de tv; Por servicio de fono; Incumplimiento visita</t>
+  </si>
+  <si>
+    <t>electrico</t>
+  </si>
+  <si>
+    <t>Fallas</t>
+  </si>
+  <si>
+    <t>¿Fallas en suministro?</t>
+  </si>
+  <si>
+    <t>generador</t>
+  </si>
+  <si>
+    <t>Generador</t>
+  </si>
+  <si>
+    <t>¿Tiene generador?</t>
+  </si>
+  <si>
+    <t>No; No realizo el soporte; No dio solución al inconveniente; Incumplimiento visita; Tuvo alguna discusión con el tecnico; Instalación deficiente; Ont en estado desconocido</t>
+  </si>
+  <si>
+    <t>INTERNET; TV HD; TV BASICA; MUNDO GO; MOVIL; VOZ IP; 3 MUNDOS (Todos los servicios)</t>
   </si>
 </sst>
 </file>
@@ -665,7 +716,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
@@ -728,6 +779,17 @@
         <v>78</v>
       </c>
     </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C7" t="s">
+        <v>102</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -735,7 +797,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D032E4CE-DA98-4447-B6EF-DADA688AB2F3}">
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1229,83 +1291,191 @@
         <v>93</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
-      <c r="A42" t="s">
+    <row r="34" spans="1:7">
+      <c r="A34" t="s">
+        <v>102</v>
+      </c>
+      <c r="B34" t="s">
+        <v>74</v>
+      </c>
+      <c r="C34" t="s">
+        <v>75</v>
+      </c>
+      <c r="D34" t="s">
+        <v>76</v>
+      </c>
+      <c r="E34" t="s">
+        <v>74</v>
+      </c>
+      <c r="G34" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" t="s">
+        <v>102</v>
+      </c>
+      <c r="B35" t="s">
+        <v>103</v>
+      </c>
+      <c r="C35" t="s">
+        <v>104</v>
+      </c>
+      <c r="D35" t="s">
+        <v>107</v>
+      </c>
+      <c r="G35" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" t="s">
+        <v>102</v>
+      </c>
+      <c r="B36" t="s">
+        <v>105</v>
+      </c>
+      <c r="C36" t="s">
+        <v>106</v>
+      </c>
+      <c r="D36" t="s">
+        <v>108</v>
+      </c>
+      <c r="G36" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" t="s">
+        <v>102</v>
+      </c>
+      <c r="B38" t="s">
+        <v>110</v>
+      </c>
+      <c r="C38" t="s">
+        <v>111</v>
+      </c>
+      <c r="D38" t="s">
+        <v>112</v>
+      </c>
+      <c r="G38" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" t="s">
+        <v>102</v>
+      </c>
+      <c r="B39" t="s">
+        <v>113</v>
+      </c>
+      <c r="C39" t="s">
+        <v>114</v>
+      </c>
+      <c r="D39" t="s">
+        <v>115</v>
+      </c>
+      <c r="G39" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" t="s">
+        <v>102</v>
+      </c>
+      <c r="B40" t="s">
+        <v>86</v>
+      </c>
+      <c r="C40" t="s">
+        <v>87</v>
+      </c>
+      <c r="D40" t="s">
+        <v>88</v>
+      </c>
+      <c r="E40" t="s">
+        <v>86</v>
+      </c>
+      <c r="G40" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" t="s">
         <v>8</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C72" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
-      <c r="A43" t="s">
+    <row r="73" spans="1:3">
+      <c r="A73" t="s">
         <v>8</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C73" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
-      <c r="A44" t="s">
+    <row r="74" spans="1:3">
+      <c r="A74" t="s">
         <v>8</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C74" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
-      <c r="A45" t="s">
+    <row r="75" spans="1:3">
+      <c r="A75" t="s">
         <v>8</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C75" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
-      <c r="A46" t="s">
+    <row r="76" spans="1:3">
+      <c r="A76" t="s">
         <v>8</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C76" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
-      <c r="A47" t="s">
+    <row r="77" spans="1:3">
+      <c r="A77" t="s">
         <v>8</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C77" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
-      <c r="A48" t="s">
+    <row r="78" spans="1:3">
+      <c r="A78" t="s">
         <v>8</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C78" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
-      <c r="A49" t="s">
+    <row r="79" spans="1:3">
+      <c r="A79" t="s">
         <v>8</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C79" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
-      <c r="A50" t="s">
+    <row r="80" spans="1:3">
+      <c r="A80" t="s">
         <v>8</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C80" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
-      <c r="A51" t="s">
+    <row r="81" spans="1:3">
+      <c r="A81" t="s">
         <v>8</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C81" t="s">
         <v>33</v>
       </c>
     </row>
